--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0001T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.73077333741081</v>
+        <v>9.706250667329257</v>
       </c>
       <c r="D2" t="n">
-        <v>64.49963680392342</v>
+        <v>10.48119098063756</v>
       </c>
       <c r="E2" t="n">
-        <v>18.3685423355226</v>
+        <v>2.984888129522423</v>
       </c>
       <c r="F2" t="n">
-        <v>16.90427694053019</v>
+        <v>2.746945002836156</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.86443826678213</v>
+        <v>2.740471218352096</v>
       </c>
       <c r="D3" t="n">
-        <v>15.81246392424133</v>
+        <v>2.569525387689216</v>
       </c>
       <c r="E3" t="n">
-        <v>18.3685423355226</v>
+        <v>2.984888129522423</v>
       </c>
       <c r="F3" t="n">
-        <v>16.90427694053019</v>
+        <v>2.746945002836156</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.82129031992812</v>
+        <v>5.17095967698832</v>
       </c>
       <c r="D4" t="n">
-        <v>32.24159612635736</v>
+        <v>5.239259370533072</v>
       </c>
       <c r="E4" t="n">
-        <v>18.3685423355226</v>
+        <v>2.984888129522423</v>
       </c>
       <c r="F4" t="n">
-        <v>16.90427694053019</v>
+        <v>2.746945002836156</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.05115718685263</v>
+        <v>3.420813042863552</v>
       </c>
       <c r="D5" t="n">
-        <v>23.92031925332085</v>
+        <v>3.887051878664638</v>
       </c>
       <c r="E5" t="n">
-        <v>18.3685423355226</v>
+        <v>2.984888129522423</v>
       </c>
       <c r="F5" t="n">
-        <v>16.90427694053019</v>
+        <v>2.746945002836156</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.684403452245203</v>
+        <v>0.9237155609898454</v>
       </c>
       <c r="D6" t="n">
-        <v>43.00126861718322</v>
+        <v>6.987706150292274</v>
       </c>
       <c r="E6" t="n">
-        <v>18.3685423355226</v>
+        <v>2.984888129522423</v>
       </c>
       <c r="F6" t="n">
-        <v>16.90427694053019</v>
+        <v>2.746945002836156</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
